--- a/data/trans_camb/IP07_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP07_R-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-11,75</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-6,7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,53</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-6,77</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-11,03</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-7,88</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-11,75</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-6,7</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>-6,11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,28</t>
+          <t>-3,14</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 5,04</t>
+          <t>-24,78; 1,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,15; 3,6</t>
+          <t>-19,49; 7,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,26; 5,29</t>
+          <t>-13,14; 12,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,45; 0,7</t>
+          <t>-19,37; 6,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,18; 5,95</t>
+          <t>-23,91; 2,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 13,88</t>
+          <t>-19,24; 7,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 0,53</t>
+          <t>-18,5; -0,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,29; -0,16</t>
+          <t>-18,03; 0,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 6,51</t>
+          <t>-12,51; 5,71</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-15,49%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-8,83%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-0,7%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-8,59%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-14,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-10,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-15,49%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-8,83%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>-7,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-4,24%</t>
+          <t>-4,07%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 6,47</t>
+          <t>-30,84; 1,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,09; 4,82</t>
+          <t>-23,92; 10,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-32,9; 6,53</t>
+          <t>-16,2; 18,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,52; 0,92</t>
+          <t>-23,18; 9,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,77; 8,08</t>
+          <t>-28,8; 2,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 20,34</t>
+          <t>-22,57; 10,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,53; 0,74</t>
+          <t>-22,77; -0,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,41; -0,2</t>
+          <t>-22,22; 0,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,13; 8,67</t>
+          <t>-15,39; 8,09</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,91</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,09</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,22</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-1,44</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>14,81</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7,17</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,91</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,09</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,59</t>
+          <t>2,36</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>3,36</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 8,14</t>
+          <t>-6,7; 11,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,27; 23,1</t>
+          <t>0,97; 17,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 17,77</t>
+          <t>-5,1; 13,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 11,88</t>
+          <t>-10,91; 8,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 18,65</t>
+          <t>6,28; 23,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 13,6</t>
+          <t>-7,22; 13,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 6,73</t>
+          <t>-6,61; 6,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,04; 18,21</t>
+          <t>5,95; 17,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 13,24</t>
+          <t>-3,49; 10,81</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11,97%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-1,91%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>19,62%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9,5%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,97%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 11,6</t>
+          <t>-8,39; 15,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,91; 33,3</t>
+          <t>1,3; 25,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 25,38</t>
+          <t>-6,39; 19,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 16,92</t>
+          <t>-13,82; 11,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 27,13</t>
+          <t>7,97; 34,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 19,47</t>
+          <t>-8,94; 19,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 9,23</t>
+          <t>-8,46; 9,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,7; 25,44</t>
+          <t>7,53; 24,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 18,27</t>
+          <t>-4,46; 15,06</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-6,48</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19,89</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11,75</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-12,3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>17,47</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9,93</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-6,48</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>19,89</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,74</t>
+          <t>10,07</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-24,87; 0,96</t>
+          <t>-18,19; 4,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,53; 28,68</t>
+          <t>11,92; 29,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 21,7</t>
+          <t>2,34; 22,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 5,09</t>
+          <t>-25,19; 0,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,77; 28,16</t>
+          <t>7,23; 27,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 21,99</t>
+          <t>-1,76; 21,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-18,78; -0,07</t>
+          <t>-19,08; 0,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,08; 25,65</t>
+          <t>11,83; 25,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 18,89</t>
+          <t>2,85; 18,24</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-8,51%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>26,14%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15,44%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-16,48%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>23,41%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>13,31%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-8,51%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>26,14%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,05; 1,81</t>
+          <t>-22,88; 6,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,7; 44,05</t>
+          <t>14,41; 42,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 31,75</t>
+          <t>2,86; 32,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 7,1</t>
+          <t>-31,98; 0,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,33; 41,12</t>
+          <t>9,13; 41,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,18; 32,18</t>
+          <t>-2,04; 31,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,73; -0,01</t>
+          <t>-24,27; 0,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,86; 36,7</t>
+          <t>14,83; 36,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,67; 26,99</t>
+          <t>3,46; 25,73</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12,36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-20,34</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5,08</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>7,43</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-15,21</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>14,92</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>12,36</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-20,34</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,88</t>
+          <t>14,44</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9,05</t>
+          <t>9,75</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 18,04</t>
+          <t>0,73; 22,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-27,14; -2,91</t>
+          <t>-31,28; -7,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,48; 25,46</t>
+          <t>-22,13; 20,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 22,6</t>
+          <t>-3,61; 18,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-33,86; -7,1</t>
+          <t>-26,07; -1,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,72; 20,4</t>
+          <t>2,44; 24,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 17,47</t>
+          <t>2,02; 18,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-27,08; -7,5</t>
+          <t>-26,88; -8,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 18,44</t>
+          <t>-5,68; 19,98</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>18,11%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-29,81%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>10,3%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-21,08%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>20,67%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>18,11%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-29,81%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 27,95</t>
+          <t>1,42; 36,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,19; -4,99</t>
+          <t>-43,76; -11,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,89; 40,86</t>
+          <t>-31,44; 32,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 37,01</t>
+          <t>-4,24; 28,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,58; -11,55</t>
+          <t>-34,76; -2,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,5; 31,42</t>
+          <t>3,39; 37,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,75; 26,86</t>
+          <t>2,91; 28,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-36,95; -12,44</t>
+          <t>-36,34; -12,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 27,14</t>
+          <t>-7,56; 29,56</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-8,94</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>19,75</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-49,17</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-2,98</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>13,41</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-58,66</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-8,94</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>19,75</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-47,54</t>
+          <t>-57,84</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-52,82</t>
+          <t>-53,35</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 9,73</t>
+          <t>-23,52; 8,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,68; 24,75</t>
+          <t>8,98; 30,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-72,26; -43,97</t>
+          <t>-64,23; -35,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-23,79; 7,12</t>
+          <t>-16,37; 10,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,85; 31,85</t>
+          <t>4,93; 24,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-61,37; -31,26</t>
+          <t>-72,37; -42,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 5,47</t>
+          <t>-15,65; 3,91</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,42; 24,38</t>
+          <t>9,12; 24,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-62,45; -41,87</t>
+          <t>-62,87; -42,13</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-11,74%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>25,93%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-64,56%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-3,57%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>16,03%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-70,16%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-11,74%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>25,93%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-62,43%</t>
+          <t>-69,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-66,23%</t>
+          <t>-66,89%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 12,73</t>
+          <t>-29,12; 12,25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5,22; 33,84</t>
+          <t>11,04; 47,65</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,84; -55,46</t>
+          <t>-77,87; -48,81</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-29,12; 10,38</t>
+          <t>-18,54; 13,89</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,45; 48,53</t>
+          <t>5,35; 33,68</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-76,08; -44,85</t>
+          <t>-82,27; -52,59</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 7,16</t>
+          <t>-18,92; 5,34</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9,91; 33,0</t>
+          <t>10,57; 33,1</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-76,08; -55,4</t>
+          <t>-76,65; -56,4</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-18,05</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>17,52</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>11,68</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-15,5</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>16,67</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>13,87</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-18,05</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>17,52</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,9</t>
+          <t>13,7</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12,81</t>
+          <t>12,66</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-28,98; -1,5</t>
+          <t>-31,92; -4,68</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>7,31; 26,81</t>
+          <t>7,71; 26,05</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3,17; 24,04</t>
+          <t>1,91; 21,74</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-30,67; -3,85</t>
+          <t>-29,46; -2,17</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,99; 27,2</t>
+          <t>7,01; 27,28</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,38; 22,47</t>
+          <t>3,49; 24,97</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-26,68; -7,26</t>
+          <t>-26,07; -7,23</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>10,44; 23,46</t>
+          <t>10,85; 23,94</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,68; 20,16</t>
+          <t>5,34; 20,16</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-22,66%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>21,99%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>14,67%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-19,6%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>21,08%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>17,53%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-22,66%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>21,99%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-34,96; -2,07</t>
+          <t>-37,31; -6,27</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8,92; 38,73</t>
+          <t>9,38; 36,47</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3,97; 33,89</t>
+          <t>2,47; 30,34</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-37,23; -5,3</t>
+          <t>-35,75; -3,45</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10,73; 39,02</t>
+          <t>8,79; 40,68</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,83; 30,73</t>
+          <t>4,17; 35,51</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-32,06; -9,61</t>
+          <t>-32,05; -9,52</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>12,81; 31,83</t>
+          <t>13,14; 33,04</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6,93; 27,57</t>
+          <t>6,38; 27,81</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-11,42</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>8,02</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0,45</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-10,77</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>10,32</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-2,2</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-11,42</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>8,02</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,02</t>
+          <t>-3,12</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,38</t>
+          <t>-1,12</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-19,6; -2,02</t>
+          <t>-19,14; -3,22</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,68; 17,09</t>
+          <t>2,6; 14,8</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 6,58</t>
+          <t>-6,47; 7,71</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-19,87; -3,85</t>
+          <t>-19,17; -2,43</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,37; 14,15</t>
+          <t>3,8; 17,81</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 6,1</t>
+          <t>-11,82; 5,18</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-17,07; -5,57</t>
+          <t>-17,14; -5,34</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>4,4; 13,21</t>
+          <t>4,99; 14,2</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 4,76</t>
+          <t>-6,24; 4,01</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-13,38%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-13,2%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>12,64%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-2,7%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-13,38%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-1,2%</t>
+          <t>-3,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-1,65%</t>
+          <t>-1,34%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-23,17; -2,63</t>
+          <t>-21,52; -4,13</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>4,33; 22,59</t>
+          <t>2,94; 18,32</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 8,31</t>
+          <t>-7,19; 9,52</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-22,76; -4,82</t>
+          <t>-22,53; -3,07</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,66; 17,49</t>
+          <t>4,25; 23,19</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 7,61</t>
+          <t>-13,91; 6,77</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-19,97; -6,91</t>
+          <t>-20,04; -6,63</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>5,35; 16,43</t>
+          <t>5,81; 17,63</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 5,78</t>
+          <t>-7,24; 5,01</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>9,54</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>20,23</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-6,13</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>9,56</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>17,85</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-3,62</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>9,54</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>20,23</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-6,15</t>
+          <t>-2,87</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-5,11</t>
+          <t>-4,67</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,81; 16,04</t>
+          <t>1,42; 16,17</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>12,35; 24,26</t>
+          <t>14,11; 26,89</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 4,18</t>
+          <t>-14,8; 2,13</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,17; 15,95</t>
+          <t>3,21; 17,09</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>14,02; 26,38</t>
+          <t>12,45; 23,98</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 2,33</t>
+          <t>-11,77; 5,93</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,52; 14,41</t>
+          <t>3,99; 14,33</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>14,65; 22,88</t>
+          <t>14,63; 23,49</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 0,85</t>
+          <t>-10,93; 1,21</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>12,93%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>27,43%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-8,31%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>12,42%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>23,18%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-4,7%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>12,93%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>27,43%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-8,34%</t>
+          <t>-3,73%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-6,78%</t>
+          <t>-6,2%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2,06; 21,99</t>
+          <t>1,5; 23,2</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>15,05; 33,55</t>
+          <t>18,17; 39,7</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-14,92; 5,72</t>
+          <t>-19,44; 3,01</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1,53; 22,64</t>
+          <t>3,82; 23,38</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>17,99; 38,34</t>
+          <t>15,46; 33,87</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 3,21</t>
+          <t>-14,93; 8,11</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,89; 20,04</t>
+          <t>5,09; 19,93</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>18,53; 31,7</t>
+          <t>18,78; 32,82</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 1,39</t>
+          <t>-14,2; 1,67</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-1,96</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>9,22</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-0,95</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-2,35</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>9,59</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-1,96</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>9,22</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>-1,17</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>-1,07</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 1,33</t>
+          <t>-5,67; 1,51</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>6,36; 12,83</t>
+          <t>5,87; 12,63</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 3,8</t>
+          <t>-5,05; 3,03</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 1,81</t>
+          <t>-5,88; 1,71</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>6,05; 13,12</t>
+          <t>6,28; 12,78</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 3,04</t>
+          <t>-4,84; 2,61</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 0,35</t>
+          <t>-4,84; 0,44</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>7,06; 11,58</t>
+          <t>7,12; 11,62</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 2,19</t>
+          <t>-4,14; 1,47</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-2,55%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>12,03%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-1,24%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-3,03%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>12,36%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-0,4%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-2,55%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>12,03%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-0,79%</t>
+          <t>-1,51%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-0,63%</t>
+          <t>-1,39%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 1,77</t>
+          <t>-7,18; 1,99</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>7,97; 16,88</t>
+          <t>7,43; 16,83</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 4,99</t>
+          <t>-6,59; 4,06</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 2,38</t>
+          <t>-7,47; 2,23</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>7,76; 17,75</t>
+          <t>7,94; 16,92</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 3,99</t>
+          <t>-6,09; 3,41</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 0,47</t>
+          <t>-6,17; 0,59</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>9,07; 15,35</t>
+          <t>9,15; 15,38</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 2,89</t>
+          <t>-5,37; 1,92</t>
         </is>
       </c>
     </row>
